--- a/data-manipulation-scripts/sheets-cleanup/sheets/ANEL ELASTICO COROA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ANEL ELASTICO COROA.xlsx
@@ -363,7 +363,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="D2" s="4">
         <v>10.0</v>
@@ -399,7 +399,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="4">
-        <v>1.0</v>
+        <v>20.0</v>
       </c>
       <c r="D3" s="4">
         <v>10.0</v>
